--- a/STOCK INVENTORY.xlsx
+++ b/STOCK INVENTORY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/DFB7DCCC86718537/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0D51FCB-CD71-4783-BEBB-4B7115011E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9EB30E2-B01C-46AB-A426-649013726C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{08D46979-87AD-44BD-9F05-3438FA1E543E}"/>
   </bookViews>
@@ -1492,7 +1492,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1570,6 +1570,7 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2022,7 +2023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CFEC72F-24CA-479E-B294-1848ADF71475}">
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -2030,6 +2031,9 @@
     <col min="4" max="4" width="73.7109375" style="16" customWidth="1"/>
     <col min="5" max="5" width="11.140625" customWidth="1"/>
     <col min="6" max="6" width="23.5703125" style="17" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="11" max="11" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2053,14 +2057,14 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="B3" t="s">
@@ -3254,7 +3258,7 @@
         <v>10226748.4</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="14.45" customHeight="1">
+    <row r="81" spans="1:8" ht="14.45" customHeight="1">
       <c r="A81" s="28" t="s">
         <v>163</v>
       </c>
@@ -3266,7 +3270,7 @@
       </c>
       <c r="F81" s="28"/>
     </row>
-    <row r="82" spans="1:6" ht="28.9" customHeight="1">
+    <row r="82" spans="1:8" ht="28.9" customHeight="1">
       <c r="B82" t="s">
         <v>164</v>
       </c>
@@ -3279,11 +3283,13 @@
       <c r="E82">
         <v>10</v>
       </c>
-      <c r="F82" s="17">
-        <v>550000</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="28.9" customHeight="1">
+      <c r="F82">
+        <v>770000</v>
+      </c>
+      <c r="G82" s="29"/>
+      <c r="H82" s="29"/>
+    </row>
+    <row r="83" spans="1:8" ht="28.9" customHeight="1">
       <c r="B83" t="s">
         <v>164</v>
       </c>
@@ -3296,11 +3302,13 @@
       <c r="E83">
         <v>10</v>
       </c>
-      <c r="F83" s="17">
-        <v>1300000</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="28.9" customHeight="1">
+      <c r="F83">
+        <v>1820000</v>
+      </c>
+      <c r="G83" s="29"/>
+      <c r="H83" s="29"/>
+    </row>
+    <row r="84" spans="1:8" ht="28.9" customHeight="1">
       <c r="B84" t="s">
         <v>164</v>
       </c>
@@ -3313,11 +3321,13 @@
       <c r="E84">
         <v>10</v>
       </c>
-      <c r="F84" s="17">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="28.9" customHeight="1">
+      <c r="F84">
+        <v>2100000</v>
+      </c>
+      <c r="G84" s="29"/>
+      <c r="H84" s="29"/>
+    </row>
+    <row r="85" spans="1:8" ht="28.9" customHeight="1">
       <c r="B85" t="s">
         <v>164</v>
       </c>
@@ -3330,11 +3340,13 @@
       <c r="E85">
         <v>10</v>
       </c>
-      <c r="F85" s="17">
-        <v>2200000</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="14.45" customHeight="1">
+      <c r="F85">
+        <v>3080000</v>
+      </c>
+      <c r="G85" s="29"/>
+      <c r="H85" s="29"/>
+    </row>
+    <row r="86" spans="1:8" ht="14.45" customHeight="1">
       <c r="B86" t="s">
         <v>164</v>
       </c>
@@ -3344,11 +3356,13 @@
       <c r="E86">
         <v>10</v>
       </c>
-      <c r="F86" s="17">
-        <v>2300000</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="14.45" customHeight="1">
+      <c r="F86">
+        <v>3220000</v>
+      </c>
+      <c r="G86" s="29"/>
+      <c r="H86" s="29"/>
+    </row>
+    <row r="87" spans="1:8" ht="14.45" customHeight="1">
       <c r="B87" t="s">
         <v>164</v>
       </c>
@@ -3358,11 +3372,13 @@
       <c r="E87">
         <v>10</v>
       </c>
-      <c r="F87" s="17">
-        <v>2300000</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="14.45" customHeight="1">
+      <c r="F87">
+        <v>3220000</v>
+      </c>
+      <c r="G87" s="29"/>
+      <c r="H87" s="29"/>
+    </row>
+    <row r="88" spans="1:8" ht="14.45" customHeight="1">
       <c r="B88" t="s">
         <v>164</v>
       </c>
@@ -3372,11 +3388,13 @@
       <c r="E88">
         <v>10</v>
       </c>
-      <c r="F88" s="17">
-        <v>3200000</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="14.45" customHeight="1">
+      <c r="F88">
+        <v>4480000</v>
+      </c>
+      <c r="G88" s="29"/>
+      <c r="H88" s="29"/>
+    </row>
+    <row r="89" spans="1:8" ht="14.45" customHeight="1">
       <c r="B89" t="s">
         <v>164</v>
       </c>
@@ -3386,11 +3404,13 @@
       <c r="E89">
         <v>10</v>
       </c>
-      <c r="F89" s="17">
-        <v>3200000</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="14.45" customHeight="1">
+      <c r="F89">
+        <v>4480000</v>
+      </c>
+      <c r="G89" s="29"/>
+      <c r="H89" s="29"/>
+    </row>
+    <row r="90" spans="1:8" ht="14.45" customHeight="1">
       <c r="B90" t="s">
         <v>164</v>
       </c>
@@ -3400,11 +3420,13 @@
       <c r="E90">
         <v>10</v>
       </c>
-      <c r="F90" s="17">
-        <v>3900000</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="14.45" customHeight="1">
+      <c r="F90">
+        <v>5460000</v>
+      </c>
+      <c r="G90" s="29"/>
+      <c r="H90" s="29"/>
+    </row>
+    <row r="91" spans="1:8" ht="14.45" customHeight="1">
       <c r="B91" t="s">
         <v>164</v>
       </c>
@@ -3414,11 +3436,13 @@
       <c r="E91">
         <v>10</v>
       </c>
-      <c r="F91" s="17">
-        <v>3200000</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="14.45" customHeight="1">
+      <c r="F91">
+        <v>4480000</v>
+      </c>
+      <c r="G91" s="29"/>
+      <c r="H91" s="29"/>
+    </row>
+    <row r="92" spans="1:8" ht="14.45" customHeight="1">
       <c r="B92" t="s">
         <v>164</v>
       </c>
@@ -3428,11 +3452,13 @@
       <c r="E92">
         <v>10</v>
       </c>
-      <c r="F92" s="17">
-        <v>4600000</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="42" customHeight="1">
+      <c r="F92">
+        <v>6440000</v>
+      </c>
+      <c r="G92" s="29"/>
+      <c r="H92" s="29"/>
+    </row>
+    <row r="93" spans="1:8" ht="42" customHeight="1">
       <c r="C93" s="24" t="s">
         <v>180</v>
       </c>
@@ -3442,11 +3468,13 @@
       <c r="E93">
         <v>10</v>
       </c>
-      <c r="F93" s="17">
-        <v>5900000</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="42" customHeight="1">
+      <c r="F93">
+        <v>8260000</v>
+      </c>
+      <c r="G93" s="29"/>
+      <c r="H93" s="29"/>
+    </row>
+    <row r="94" spans="1:8" ht="42" customHeight="1">
       <c r="C94" s="24" t="s">
         <v>182</v>
       </c>
@@ -3456,11 +3484,13 @@
       <c r="E94">
         <v>10</v>
       </c>
-      <c r="F94" s="17">
-        <v>9000000</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="14.45" customHeight="1">
+      <c r="F94">
+        <v>12600000</v>
+      </c>
+      <c r="G94" s="29"/>
+      <c r="H94" s="29"/>
+    </row>
+    <row r="95" spans="1:8" ht="14.45" customHeight="1">
       <c r="C95" s="8" t="s">
         <v>184</v>
       </c>
@@ -3468,11 +3498,13 @@
       <c r="E95">
         <v>10</v>
       </c>
-      <c r="F95" s="17">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="28.9" customHeight="1">
+      <c r="F95">
+        <v>1190000</v>
+      </c>
+      <c r="G95" s="29"/>
+      <c r="H95" s="29"/>
+    </row>
+    <row r="96" spans="1:8" ht="28.9" customHeight="1">
       <c r="C96" t="s">
         <v>185</v>
       </c>
@@ -3482,11 +3514,13 @@
       <c r="E96">
         <v>10</v>
       </c>
-      <c r="F96" s="17">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="97" spans="3:6" ht="28.9" customHeight="1">
+      <c r="F96">
+        <v>1190000</v>
+      </c>
+      <c r="G96" s="29"/>
+      <c r="H96" s="29"/>
+    </row>
+    <row r="97" spans="3:8" ht="28.9" customHeight="1">
       <c r="C97" t="s">
         <v>187</v>
       </c>
@@ -3496,11 +3530,13 @@
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="F97" s="17">
-        <v>1700000</v>
-      </c>
-    </row>
-    <row r="98" spans="3:6" ht="28.9" customHeight="1">
+      <c r="F97">
+        <v>2380000</v>
+      </c>
+      <c r="G97" s="29"/>
+      <c r="H97" s="29"/>
+    </row>
+    <row r="98" spans="3:8" ht="28.9" customHeight="1">
       <c r="C98" t="s">
         <v>189</v>
       </c>
@@ -3510,11 +3546,13 @@
       <c r="E98">
         <v>10</v>
       </c>
-      <c r="F98" s="17">
-        <v>2100000</v>
-      </c>
-    </row>
-    <row r="99" spans="3:6" ht="14.45" customHeight="1">
+      <c r="F98">
+        <v>2940000</v>
+      </c>
+      <c r="G98" s="29"/>
+      <c r="H98" s="29"/>
+    </row>
+    <row r="99" spans="3:8" ht="14.45" customHeight="1">
       <c r="C99" t="s">
         <v>191</v>
       </c>
@@ -3524,33 +3562,39 @@
       <c r="E99">
         <v>10</v>
       </c>
-      <c r="F99" s="17">
-        <v>2600000</v>
-      </c>
-    </row>
-    <row r="100" spans="3:6" ht="14.45" customHeight="1">
+      <c r="F99">
+        <v>3640000</v>
+      </c>
+      <c r="G99" s="29"/>
+      <c r="H99" s="29"/>
+    </row>
+    <row r="100" spans="3:8" ht="14.45" customHeight="1">
       <c r="C100" t="s">
         <v>193</v>
       </c>
       <c r="E100">
         <v>10</v>
       </c>
-      <c r="F100" s="17">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="101" spans="3:6" ht="14.45" customHeight="1">
+      <c r="F100">
+        <v>1540000</v>
+      </c>
+      <c r="G100" s="29"/>
+      <c r="H100" s="29"/>
+    </row>
+    <row r="101" spans="3:8" ht="14.45" customHeight="1">
       <c r="C101" t="s">
         <v>194</v>
       </c>
       <c r="E101">
         <v>10</v>
       </c>
-      <c r="F101" s="17">
-        <v>1100000</v>
-      </c>
-    </row>
-    <row r="102" spans="3:6" ht="14.45" customHeight="1">
+      <c r="F101">
+        <v>1540000</v>
+      </c>
+      <c r="G101" s="29"/>
+      <c r="H101" s="29"/>
+    </row>
+    <row r="102" spans="3:8" ht="14.45" customHeight="1">
       <c r="C102" s="24" t="s">
         <v>195</v>
       </c>
@@ -3560,11 +3604,13 @@
       <c r="E102">
         <v>10</v>
       </c>
-      <c r="F102" s="17">
-        <v>1600000</v>
-      </c>
-    </row>
-    <row r="103" spans="3:6" ht="14.45" customHeight="1">
+      <c r="F102">
+        <v>2240000</v>
+      </c>
+      <c r="G102" s="29"/>
+      <c r="H102" s="29"/>
+    </row>
+    <row r="103" spans="3:8" ht="14.45" customHeight="1">
       <c r="C103" s="24" t="s">
         <v>197</v>
       </c>
@@ -3572,11 +3618,13 @@
       <c r="E103">
         <v>10</v>
       </c>
-      <c r="F103" s="17">
-        <v>1375000</v>
-      </c>
-    </row>
-    <row r="104" spans="3:6" ht="14.45" customHeight="1">
+      <c r="F103">
+        <v>1925000</v>
+      </c>
+      <c r="G103" s="29"/>
+      <c r="H103" s="29"/>
+    </row>
+    <row r="104" spans="3:8" ht="14.45" customHeight="1">
       <c r="C104" s="21" t="s">
         <v>198</v>
       </c>
@@ -3584,39 +3632,41 @@
       <c r="E104">
         <v>10</v>
       </c>
-      <c r="F104" s="17">
-        <v>10400000</v>
-      </c>
-    </row>
-    <row r="105" spans="3:6" ht="15">
+      <c r="F104">
+        <v>14560000</v>
+      </c>
+      <c r="G104" s="29"/>
+      <c r="H104" s="29"/>
+    </row>
+    <row r="105" spans="3:8" ht="15">
       <c r="C105" s="21"/>
       <c r="D105" s="15"/>
     </row>
-    <row r="106" spans="3:6">
+    <row r="106" spans="3:8">
       <c r="C106" s="24"/>
       <c r="D106" s="15"/>
     </row>
-    <row r="107" spans="3:6">
+    <row r="107" spans="3:8">
       <c r="C107" s="21"/>
       <c r="D107" s="14"/>
     </row>
-    <row r="108" spans="3:6">
+    <row r="108" spans="3:8">
       <c r="C108" s="21"/>
       <c r="D108" s="15"/>
     </row>
-    <row r="109" spans="3:6">
+    <row r="109" spans="3:8">
       <c r="C109" s="21"/>
       <c r="D109" s="15"/>
     </row>
-    <row r="110" spans="3:6">
+    <row r="110" spans="3:8">
       <c r="C110" s="21"/>
       <c r="D110" s="15"/>
     </row>
-    <row r="111" spans="3:6">
+    <row r="111" spans="3:8">
       <c r="C111" s="21"/>
       <c r="D111" s="15"/>
     </row>
-    <row r="112" spans="3:6">
+    <row r="112" spans="3:8">
       <c r="C112" s="21"/>
       <c r="D112" s="15"/>
     </row>
@@ -3645,12 +3695,12 @@
       <c r="D118" s="23"/>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="29"/>
-      <c r="B119" s="29"/>
-      <c r="C119" s="29"/>
-      <c r="D119" s="29"/>
-      <c r="E119" s="29"/>
-      <c r="F119" s="29"/>
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="30"/>
+      <c r="D119" s="30"/>
+      <c r="E119" s="30"/>
+      <c r="F119" s="30"/>
     </row>
     <row r="120" spans="1:6">
       <c r="C120" s="6"/>
@@ -3693,12 +3743,12 @@
       <c r="D129" s="22"/>
     </row>
     <row r="130" spans="1:6">
-      <c r="A130" s="29"/>
-      <c r="B130" s="29"/>
-      <c r="C130" s="29"/>
-      <c r="D130" s="29"/>
-      <c r="E130" s="29"/>
-      <c r="F130" s="29"/>
+      <c r="A130" s="30"/>
+      <c r="B130" s="30"/>
+      <c r="C130" s="30"/>
+      <c r="D130" s="30"/>
+      <c r="E130" s="30"/>
+      <c r="F130" s="30"/>
     </row>
     <row r="131" spans="1:6">
       <c r="C131" s="19"/>
